--- a/data/export/2026-10-15-operations.xlsx
+++ b/data/export/2026-10-15-operations.xlsx
@@ -427,13 +427,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -643,32 +643,36 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -676,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -700,33 +704,37 @@
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
@@ -759,32 +767,36 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:22</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -792,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -816,17 +828,17 @@
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -836,13 +848,17 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/13</t>
         </is>
       </c>
     </row>
@@ -875,32 +891,36 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -908,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -932,33 +952,37 @@
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
@@ -1024,7 +1048,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1063,7 +1087,7 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1074,7 +1098,7 @@
       <c r="AC5" s="2" t="inlineStr"/>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1107,32 +1131,36 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1140,7 +1168,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1164,17 +1192,17 @@
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1184,13 +1212,17 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>4/13</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1288,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1306,7 +1338,7 @@
       <c r="AC7" s="2" t="inlineStr"/>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1404,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1422,7 +1454,7 @@
       <c r="AC8" s="2" t="inlineStr"/>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1520,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1538,7 +1570,7 @@
       <c r="AC9" s="2" t="inlineStr"/>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -1551,22 +1583,22 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>沪A13735A</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1599,12 +1631,12 @@
       <c r="N10" s="2" t="inlineStr"/>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:02</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>06:22</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1618,7 +1650,7 @@
       <c r="U10" s="2" t="inlineStr"/>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1654,35 +1686,35 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1715,12 +1747,12 @@
       <c r="N11" s="2" t="inlineStr"/>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1734,7 +1766,7 @@
       <c r="U11" s="2" t="inlineStr"/>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1770,35 +1802,35 @@
       <c r="AC11" s="2" t="inlineStr"/>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr"/>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1831,12 +1863,12 @@
       <c r="N12" s="2" t="inlineStr"/>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1850,7 +1882,7 @@
       <c r="U12" s="2" t="inlineStr"/>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -1886,35 +1918,35 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr"/>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1947,12 +1979,12 @@
       <c r="N13" s="2" t="inlineStr"/>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1966,7 +1998,7 @@
       <c r="U13" s="2" t="inlineStr"/>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1991,46 +2023,50 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>3/13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr"/>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2063,12 +2099,12 @@
       <c r="N14" s="2" t="inlineStr"/>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2082,7 +2118,7 @@
       <c r="U14" s="2" t="inlineStr"/>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2118,35 +2154,35 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr"/>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2179,12 +2215,12 @@
       <c r="N15" s="2" t="inlineStr"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2198,7 +2234,7 @@
       <c r="U15" s="2" t="inlineStr"/>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -2234,35 +2270,35 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr"/>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2295,12 +2331,12 @@
       <c r="N16" s="2" t="inlineStr"/>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2314,7 +2350,7 @@
       <c r="U16" s="2" t="inlineStr"/>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>07:55</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2339,46 +2375,50 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>2/13</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2411,12 +2451,12 @@
       <c r="N17" s="2" t="inlineStr"/>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2430,7 +2470,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2455,7 +2495,7 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
@@ -2466,7 +2506,7 @@
       <c r="AC17" s="2" t="inlineStr"/>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/13</t>
         </is>
       </c>
     </row>
@@ -2479,22 +2519,22 @@
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2527,12 +2567,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2546,7 +2586,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2582,25 +2622,25 @@
       <c r="AC18" s="2" t="inlineStr"/>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/8</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2610,41 +2650,37 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2652,7 +2688,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2676,17 +2712,17 @@
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2696,45 +2732,41 @@
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr"/>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2772,7 +2804,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2786,7 +2818,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2822,35 +2854,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2888,7 +2920,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2902,7 +2934,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2938,35 +2970,35 @@
       <c r="AC21" s="2" t="inlineStr"/>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2999,12 +3031,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3018,7 +3050,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3054,7 +3086,3603 @@
       <c r="AC22" s="2" t="inlineStr"/>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr"/>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>沪A55102D</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>06:11</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AD23" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr"/>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>沪A71572D</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AD24" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr"/>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>沪A37823D</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr"/>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr"/>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr"/>
+      <c r="AD25" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr"/>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>沪A70597D</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr"/>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AD26" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>沪A37267D</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr"/>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AD27" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr"/>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>沪A95621D</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr"/>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr"/>
+      <c r="AD28" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr"/>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>沪A68375D</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr"/>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AD29" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr"/>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>沪A51682D</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr"/>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr"/>
+      <c r="AD30" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr"/>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>沪A62880D</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr"/>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr"/>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr"/>
+      <c r="AD31" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr"/>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>沪A62217D</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr"/>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr"/>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr"/>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>沪A02891D</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr"/>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr"/>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr"/>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr"/>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>沪A15790A</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr"/>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr"/>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr"/>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr"/>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>沪A11062A</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr"/>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr"/>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr"/>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>沪A72873D</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr"/>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr"/>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr"/>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr"/>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr"/>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>沪A67712D</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr"/>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>—/20</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr"/>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr"/>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr"/>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr"/>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr"/>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr"/>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr"/>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr"/>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr"/>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr"/>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr"/>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr"/>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr"/>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr"/>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr"/>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr"/>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr"/>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr"/>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr"/>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr"/>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr"/>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr"/>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr"/>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr"/>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr"/>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr"/>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr"/>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr"/>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr"/>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr"/>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr"/>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr"/>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr"/>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr"/>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr"/>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr"/>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr"/>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr"/>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr"/>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr"/>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr"/>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr"/>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr"/>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr"/>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr"/>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr"/>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr"/>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr"/>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N52" s="2" t="inlineStr"/>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr"/>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr"/>
+      <c r="AD52" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr"/>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N53" s="2" t="inlineStr"/>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr"/>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr"/>
+      <c r="AD53" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-operations.xlsx
+++ b/data/export/2026-10-15-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD53"/>
+  <dimension ref="A1:AD81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -437,7 +437,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="35" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
@@ -447,10 +447,10 @@
     <col width="14" customWidth="1" min="15" max="15"/>
     <col width="14" customWidth="1" min="16" max="16"/>
     <col width="10" customWidth="1" min="17" max="17"/>
-    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="18" max="18"/>
     <col width="16" customWidth="1" min="19" max="19"/>
     <col width="20" customWidth="1" min="20" max="20"/>
-    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="36" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="14" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -843,14 +843,14 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
           <t>72.0</t>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>1/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -901,24 +901,24 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>07:36</t>
+          <t>07:37</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1015,32 +1015,36 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:58</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1048,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1072,17 +1076,17 @@
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1092,13 +1096,17 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1149,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr"/>
@@ -1168,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1207,22 +1215,22 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>4/13</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1263,36 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1288,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1312,33 +1324,37 @@
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1371,32 +1387,36 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr"/>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1404,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1428,33 +1448,37 @@
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1511,36 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
           <t>06:22</t>
@@ -1520,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1544,33 +1572,37 @@
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1675,7 +1707,7 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
@@ -1686,7 +1718,7 @@
       <c r="AC10" s="2" t="inlineStr"/>
       <c r="AD10" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1719,32 +1751,36 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -1752,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1776,33 +1812,37 @@
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1868,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1918,7 +1958,7 @@
       <c r="AC12" s="2" t="inlineStr"/>
       <c r="AD12" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1984,7 +2024,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2038,7 +2078,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/13</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2104,7 +2144,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2154,7 +2194,7 @@
       <c r="AC14" s="2" t="inlineStr"/>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2260,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2270,7 +2310,7 @@
       <c r="AC15" s="2" t="inlineStr"/>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2336,7 +2376,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2385,12 +2425,12 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>77.0</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/13</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2403,22 +2443,22 @@
       <c r="B17" s="2" t="inlineStr"/>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>08:15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2456,7 +2496,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2470,7 +2510,7 @@
       <c r="U17" s="2" t="inlineStr"/>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>08:15</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2500,41 +2540,45 @@
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>72.0</t>
+        </is>
+      </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>—/13</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr"/>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2567,12 +2611,12 @@
       <c r="N18" s="2" t="inlineStr"/>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2586,7 +2630,7 @@
       <c r="U18" s="2" t="inlineStr"/>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
@@ -2611,46 +2655,50 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr"/>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2683,12 +2731,12 @@
       <c r="N19" s="2" t="inlineStr"/>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2702,7 +2750,7 @@
       <c r="U19" s="2" t="inlineStr"/>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:15</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -2727,46 +2775,50 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr"/>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A31963D</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2799,12 +2851,12 @@
       <c r="N20" s="2" t="inlineStr"/>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:52</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2818,7 +2870,7 @@
       <c r="U20" s="2" t="inlineStr"/>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2854,35 +2906,35 @@
       <c r="AC20" s="2" t="inlineStr"/>
       <c r="AD20" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr"/>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68397D</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2915,12 +2967,12 @@
       <c r="N21" s="2" t="inlineStr"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2934,7 +2986,7 @@
       <c r="U21" s="2" t="inlineStr"/>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2959,46 +3011,50 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr"/>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -3031,12 +3087,12 @@
       <c r="N22" s="2" t="inlineStr"/>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3050,7 +3106,7 @@
       <c r="U22" s="2" t="inlineStr"/>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3075,46 +3131,50 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr"/>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3147,12 +3207,12 @@
       <c r="N23" s="2" t="inlineStr"/>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3166,7 +3226,7 @@
       <c r="U23" s="2" t="inlineStr"/>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3191,46 +3251,50 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr"/>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3263,12 +3327,12 @@
       <c r="N24" s="2" t="inlineStr"/>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3282,7 +3346,7 @@
       <c r="U24" s="2" t="inlineStr"/>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3307,46 +3371,50 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr"/>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3379,12 +3447,12 @@
       <c r="N25" s="2" t="inlineStr"/>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3398,7 +3466,7 @@
       <c r="U25" s="2" t="inlineStr"/>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3423,7 +3491,7 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3434,7 +3502,7 @@
       <c r="AC25" s="2" t="inlineStr"/>
       <c r="AD25" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -3447,60 +3515,64 @@
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3514,7 +3586,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3524,33 +3596,37 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -3563,60 +3639,64 @@
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3630,7 +3710,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3640,33 +3720,37 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3679,60 +3763,64 @@
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3746,7 +3834,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3756,17 +3844,17 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3776,13 +3864,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -3795,7 +3887,7 @@
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -3805,7 +3897,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3815,40 +3907,44 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>153分钟</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3862,7 +3958,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3872,33 +3968,37 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB29" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC29" s="2" t="inlineStr"/>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -3911,7 +4011,7 @@
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -3921,7 +4021,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -3931,12 +4031,12 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -3959,12 +4059,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3972,13 +4072,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr"/>
-      <c r="S30" s="2" t="inlineStr"/>
-      <c r="T30" s="2" t="inlineStr"/>
-      <c r="U30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4014,7 +4130,7 @@
       <c r="AC30" s="2" t="inlineStr"/>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4027,22 +4143,22 @@
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4075,12 +4191,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4094,7 +4210,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4130,7 +4246,7 @@
       <c r="AC31" s="2" t="inlineStr"/>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4143,7 +4259,7 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -4153,7 +4269,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -4191,12 +4307,12 @@
       <c r="N32" s="2" t="inlineStr"/>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4210,7 +4326,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4246,7 +4362,7 @@
       <c r="AC32" s="2" t="inlineStr"/>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4259,22 +4375,22 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4307,12 +4423,12 @@
       <c r="N33" s="2" t="inlineStr"/>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4326,7 +4442,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4362,7 +4478,7 @@
       <c r="AC33" s="2" t="inlineStr"/>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4375,22 +4491,22 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4423,12 +4539,12 @@
       <c r="N34" s="2" t="inlineStr"/>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4442,7 +4558,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4478,7 +4594,7 @@
       <c r="AC34" s="2" t="inlineStr"/>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4491,7 +4607,7 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -4501,7 +4617,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4539,12 +4655,12 @@
       <c r="N35" s="2" t="inlineStr"/>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4558,7 +4674,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4594,7 +4710,7 @@
       <c r="AC35" s="2" t="inlineStr"/>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4607,7 +4723,7 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -4617,7 +4733,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4655,12 +4771,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4674,7 +4790,7 @@
       <c r="U36" s="2" t="inlineStr"/>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4710,7 +4826,7 @@
       <c r="AC36" s="2" t="inlineStr"/>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -4723,22 +4839,22 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4771,12 +4887,12 @@
       <c r="N37" s="2" t="inlineStr"/>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4790,7 +4906,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4826,35 +4942,35 @@
       <c r="AC37" s="2" t="inlineStr"/>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/20</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4887,12 +5003,12 @@
       <c r="N38" s="2" t="inlineStr"/>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4906,7 +5022,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -4931,7 +5047,7 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
@@ -4942,35 +5058,35 @@
       <c r="AC38" s="2" t="inlineStr"/>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -5003,12 +5119,12 @@
       <c r="N39" s="2" t="inlineStr"/>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5022,7 +5138,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5058,35 +5174,35 @@
       <c r="AC39" s="2" t="inlineStr"/>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5119,12 +5235,12 @@
       <c r="N40" s="2" t="inlineStr"/>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5138,7 +5254,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5174,35 +5290,35 @@
       <c r="AC40" s="2" t="inlineStr"/>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -5235,12 +5351,12 @@
       <c r="N41" s="2" t="inlineStr"/>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:01</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5254,7 +5370,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5290,35 +5406,35 @@
       <c r="AC41" s="2" t="inlineStr"/>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5351,12 +5467,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5370,7 +5486,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5406,35 +5522,35 @@
       <c r="AC42" s="2" t="inlineStr"/>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5467,12 +5583,12 @@
       <c r="N43" s="2" t="inlineStr"/>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:41</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5486,7 +5602,7 @@
       <c r="U43" s="2" t="inlineStr"/>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5522,35 +5638,35 @@
       <c r="AC43" s="2" t="inlineStr"/>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5583,12 +5699,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5602,7 +5718,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5638,35 +5754,35 @@
       <c r="AC44" s="2" t="inlineStr"/>
       <c r="AD44" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5699,12 +5815,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5718,7 +5834,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5754,35 +5870,35 @@
       <c r="AC45" s="2" t="inlineStr"/>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5815,12 +5931,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5834,7 +5950,7 @@
       <c r="U46" s="2" t="inlineStr"/>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5870,35 +5986,35 @@
       <c r="AC46" s="2" t="inlineStr"/>
       <c r="AD46" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5931,12 +6047,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5950,7 +6066,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -5986,35 +6102,35 @@
       <c r="AC47" s="2" t="inlineStr"/>
       <c r="AD47" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6047,12 +6163,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6066,7 +6182,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6102,35 +6218,35 @@
       <c r="AC48" s="2" t="inlineStr"/>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -6168,7 +6284,7 @@
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6182,7 +6298,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6218,35 +6334,35 @@
       <c r="AC49" s="2" t="inlineStr"/>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -6279,12 +6395,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6298,7 +6414,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6334,35 +6450,35 @@
       <c r="AC50" s="2" t="inlineStr"/>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6395,12 +6511,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6414,7 +6530,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6450,35 +6566,35 @@
       <c r="AC51" s="2" t="inlineStr"/>
       <c r="AD51" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6516,7 +6632,7 @@
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6530,7 +6646,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6566,35 +6682,35 @@
       <c r="AC52" s="2" t="inlineStr"/>
       <c r="AD52" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6627,12 +6743,12 @@
       <c r="N53" s="2" t="inlineStr"/>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6646,7 +6762,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6671,7 +6787,7 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
@@ -6682,7 +6798,3327 @@
       <c r="AC53" s="2" t="inlineStr"/>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>沪A90275D</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr"/>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr"/>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
+      <c r="AD54" s="2" t="inlineStr">
+        <is>
+          <t>2/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>沪A05218D</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N55" s="2" t="inlineStr"/>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr"/>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="AD55" s="2" t="inlineStr">
+        <is>
+          <t>1/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>浦东35路</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>沪A66883D</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N56" s="2" t="inlineStr"/>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr"/>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>153.0</t>
+        </is>
+      </c>
+      <c r="AD56" s="2" t="inlineStr">
+        <is>
+          <t>4/28</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr"/>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>07:34</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>84分钟</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr"/>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD57" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr"/>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N58" s="2" t="inlineStr"/>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr"/>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr"/>
+      <c r="AD58" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr"/>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>08:24</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr">
+        <is>
+          <t>104分钟</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr"/>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD59" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr"/>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>86分钟</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr"/>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD60" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr"/>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr">
+        <is>
+          <t>91分钟</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr"/>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD61" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr"/>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N62" s="2" t="inlineStr"/>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr"/>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr"/>
+      <c r="AD62" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr"/>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr">
+        <is>
+          <t>90分钟</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr"/>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD63" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr"/>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N64" s="2" t="inlineStr"/>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr"/>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr"/>
+      <c r="AD64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr"/>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N65" s="2" t="inlineStr"/>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr"/>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AD65" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr"/>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N66" s="2" t="inlineStr"/>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr"/>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AD66" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr"/>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N67" s="2" t="inlineStr"/>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr"/>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AD67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr"/>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N68" s="2" t="inlineStr"/>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr"/>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AD68" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr"/>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N69" s="2" t="inlineStr"/>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr"/>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AD69" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr"/>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr"/>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr"/>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AD70" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr"/>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N71" s="2" t="inlineStr"/>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr"/>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr"/>
+      <c r="AD71" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr"/>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr"/>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr"/>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AD72" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr"/>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr"/>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr"/>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD73" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr"/>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr"/>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr"/>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AD74" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr"/>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N75" s="2" t="inlineStr"/>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr"/>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD75" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr"/>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr"/>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr"/>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr"/>
+      <c r="AD76" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr"/>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr"/>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr"/>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD77" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr"/>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr"/>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr"/>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD78" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr"/>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr"/>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr"/>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>08:38</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AD79" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr"/>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N80" s="2" t="inlineStr"/>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr"/>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AD80" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr"/>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N81" s="2" t="inlineStr"/>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr"/>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr"/>
+      <c r="AD81" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-operations.xlsx
+++ b/data/export/2026-10-15-operations.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -719,17 +719,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
@@ -804,7 +804,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -967,22 +967,22 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1052,7 +1052,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1091,22 +1091,22 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1176,7 +1176,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1230,7 +1230,7 @@
       </c>
       <c r="AD6" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AD9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1842,7 +1842,7 @@
       </c>
       <c r="AD11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1991,32 +1991,36 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2024,7 +2028,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2048,32 +2052,32 @@
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
@@ -2111,32 +2115,36 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -2144,7 +2152,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2168,33 +2176,37 @@
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2227,32 +2239,36 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2260,7 +2276,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2284,33 +2300,37 @@
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2363,36 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2376,7 +2400,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2400,37 +2424,37 @@
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2520,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2583,32 +2607,36 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -2616,7 +2644,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2640,37 +2668,37 @@
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2764,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2790,7 +2818,7 @@
       </c>
       <c r="AD19" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2856,7 +2884,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2972,7 +3000,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3026,7 +3054,7 @@
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3092,7 +3120,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -3146,7 +3174,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3212,7 +3240,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -3266,7 +3294,7 @@
       </c>
       <c r="AD23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3332,7 +3360,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3386,7 +3414,7 @@
       </c>
       <c r="AD24" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3452,7 +3480,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>08:22</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3509,70 +3537,66 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr"/>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A67026D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>08:16</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>126分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr"/>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3586,7 +3610,7 @@
       <c r="U26" s="2" t="inlineStr"/>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3596,17 +3620,17 @@
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3616,87 +3640,79 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC26" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr"/>
       <c r="AD26" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr"/>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A67353D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr"/>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3710,7 +3726,7 @@
       <c r="U27" s="2" t="inlineStr"/>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3720,107 +3736,103 @@
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr"/>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>沪A67672D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>08:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>140分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr"/>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3834,7 +3846,7 @@
       <c r="U28" s="2" t="inlineStr"/>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>06:26</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3844,107 +3856,103 @@
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>140.0</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr"/>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A12050A</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>09:04</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>153分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr"/>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3958,7 +3966,7 @@
       <c r="U29" s="2" t="inlineStr"/>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3968,17 +3976,17 @@
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3993,50 +4001,50 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>153.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr"/>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>沪A72305D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>疑似区间车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq36，推进8站，达到≥2站确认条件</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -4059,12 +4067,12 @@
       <c r="N30" s="2" t="inlineStr"/>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4072,29 +4080,13 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>物理seq26（站名待映射）</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
-        </is>
-      </c>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr"/>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>06:36</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
@@ -4119,46 +4111,50 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC30" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
       <c r="AD30" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>浦东35路</t>
+          <t>182路</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr"/>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>沪A55102D</t>
+          <t>沪A31073D</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>东高路张杨北路</t>
+          <t>川沙客运站</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>康恩路康浦路</t>
+          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -4191,12 +4187,12 @@
       <c r="N31" s="2" t="inlineStr"/>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>06:11</t>
+          <t>06:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -4210,7 +4206,7 @@
       <c r="U31" s="2" t="inlineStr"/>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
@@ -4235,18 +4231,22 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4259,52 +4259,56 @@
       <c r="B32" s="2" t="inlineStr"/>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>沪A71572D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>06:42</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:16</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr"/>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4312,7 +4316,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -4326,7 +4330,7 @@
       <c r="U32" s="2" t="inlineStr"/>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>06:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
@@ -4336,33 +4340,37 @@
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
@@ -4375,60 +4383,64 @@
       <c r="B33" s="2" t="inlineStr"/>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>沪A37823D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>140分钟</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr"/>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>06:31</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4442,7 +4454,7 @@
       <c r="U33" s="2" t="inlineStr"/>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
@@ -4452,33 +4464,37 @@
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB33" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>140.0</t>
+        </is>
+      </c>
       <c r="AD33" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
@@ -4491,60 +4507,64 @@
       <c r="B34" s="2" t="inlineStr"/>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>沪A70597D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>06:26</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>06:54</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>141分钟</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr"/>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4558,7 +4578,7 @@
       <c r="U34" s="2" t="inlineStr"/>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>06:54</t>
+          <t>06:26</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
@@ -4568,33 +4588,37 @@
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>141.0</t>
+        </is>
+      </c>
       <c r="AD34" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
@@ -4607,60 +4631,64 @@
       <c r="B35" s="2" t="inlineStr"/>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>沪A37267D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>06:31</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr"/>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4674,7 +4702,7 @@
       <c r="U35" s="2" t="inlineStr"/>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -4684,33 +4712,37 @@
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4723,32 +4755,32 @@
       <c r="B36" s="2" t="inlineStr"/>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>沪A95621D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>06:36</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>07:06</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq61，推进33站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -4771,12 +4803,12 @@
       <c r="N36" s="2" t="inlineStr"/>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4784,13 +4816,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
-      <c r="U36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq26映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±4分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>07:06</t>
+          <t>06:36</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4815,7 +4863,7 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4839,60 +4887,64 @@
       <c r="B37" s="2" t="inlineStr"/>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>沪A68375D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>07:12</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>151分钟</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4906,7 +4958,7 @@
       <c r="U37" s="2" t="inlineStr"/>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>07:12</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
@@ -4916,33 +4968,37 @@
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB37" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD37" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
@@ -4955,60 +5011,64 @@
       <c r="B38" s="2" t="inlineStr"/>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>沪A51682D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>06:42</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr"/>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5022,7 +5082,7 @@
       <c r="U38" s="2" t="inlineStr"/>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:42</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
@@ -5032,33 +5092,37 @@
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB38" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD38" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5071,60 +5135,64 @@
       <c r="B39" s="2" t="inlineStr"/>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>沪A62880D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>06:54</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>07:18</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>149分钟</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr"/>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5138,7 +5206,7 @@
       <c r="U39" s="2" t="inlineStr"/>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
@@ -5148,33 +5216,37 @@
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
@@ -5187,7 +5259,7 @@
       <c r="B40" s="2" t="inlineStr"/>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>沪A62217D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -5197,7 +5269,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -5207,40 +5279,44 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>163分钟</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr"/>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5254,7 +5330,7 @@
       <c r="U40" s="2" t="inlineStr"/>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>07:24</t>
+          <t>06:54</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -5264,33 +5340,37 @@
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB40" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
@@ -5303,60 +5383,64 @@
       <c r="B41" s="2" t="inlineStr"/>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>沪A02891D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
-        </is>
-      </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>147分钟</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr"/>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>08:01</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5370,7 +5454,7 @@
       <c r="U41" s="2" t="inlineStr"/>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -5380,33 +5464,37 @@
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB41" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD41" s="2" t="inlineStr">
         <is>
-          <t>—/28</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -5419,22 +5507,22 @@
       <c r="B42" s="2" t="inlineStr"/>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>沪A15790A</t>
+          <t>沪A95621D</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>07:06</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5467,12 +5555,12 @@
       <c r="N42" s="2" t="inlineStr"/>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5486,7 +5574,7 @@
       <c r="U42" s="2" t="inlineStr"/>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:06</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
@@ -5535,32 +5623,32 @@
       <c r="B43" s="2" t="inlineStr"/>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>沪A11062A</t>
+          <t>沪A68375D</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
-        </is>
-      </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq38推进至seq49，推进11站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5588,7 +5676,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>07:41</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5596,13 +5684,29 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
-      <c r="T43" s="2" t="inlineStr"/>
-      <c r="U43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>08:29</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq23映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±6分钟；反向位置物理seq38（站名待映射） ETA 8分钟参与校验</t>
+        </is>
+      </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
@@ -5651,22 +5755,22 @@
       <c r="B44" s="2" t="inlineStr"/>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>沪A72873D</t>
+          <t>沪A51682D</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>07:42</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5699,12 +5803,12 @@
       <c r="N44" s="2" t="inlineStr"/>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5718,7 +5822,7 @@
       <c r="U44" s="2" t="inlineStr"/>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
@@ -5767,22 +5871,22 @@
       <c r="B45" s="2" t="inlineStr"/>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>沪A67712D</t>
+          <t>沪A62880D</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>07:18</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>07:54</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5815,12 +5919,12 @@
       <c r="N45" s="2" t="inlineStr"/>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5834,7 +5938,7 @@
       <c r="U45" s="2" t="inlineStr"/>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
@@ -5883,7 +5987,7 @@
       <c r="B46" s="2" t="inlineStr"/>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>沪A73927D</t>
+          <t>沪A62217D</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -5893,7 +5997,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -5903,12 +6007,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程34%处后消失；随后反向物理轨迹由seq44推进至seq47，推进3站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
@@ -5931,12 +6035,12 @@
       <c r="N46" s="2" t="inlineStr"/>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5944,13 +6048,25 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr">
+        <is>
+          <t>物理seq23（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>08:39</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr"/>
-      <c r="U46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq23映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
@@ -5999,22 +6115,22 @@
       <c r="B47" s="2" t="inlineStr"/>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>沪A62981D</t>
+          <t>沪A02891D</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -6047,12 +6163,12 @@
       <c r="N47" s="2" t="inlineStr"/>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -6066,7 +6182,7 @@
       <c r="U47" s="2" t="inlineStr"/>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
@@ -6115,22 +6231,22 @@
       <c r="B48" s="2" t="inlineStr"/>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>沪A68261D</t>
+          <t>沪A15790A</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -6163,12 +6279,12 @@
       <c r="N48" s="2" t="inlineStr"/>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6182,7 +6298,7 @@
       <c r="U48" s="2" t="inlineStr"/>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
@@ -6231,7 +6347,7 @@
       <c r="B49" s="2" t="inlineStr"/>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>沪A36993D</t>
+          <t>沪A11062A</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -6241,7 +6357,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -6279,12 +6395,12 @@
       <c r="N49" s="2" t="inlineStr"/>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6298,7 +6414,7 @@
       <c r="U49" s="2" t="inlineStr"/>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
@@ -6347,7 +6463,7 @@
       <c r="B50" s="2" t="inlineStr"/>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>沪A68895D</t>
+          <t>沪A72873D</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -6357,7 +6473,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -6395,12 +6511,12 @@
       <c r="N50" s="2" t="inlineStr"/>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6414,7 +6530,7 @@
       <c r="U50" s="2" t="inlineStr"/>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
@@ -6463,22 +6579,22 @@
       <c r="B51" s="2" t="inlineStr"/>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>沪A02316D</t>
+          <t>沪A67712D</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -6511,12 +6627,12 @@
       <c r="N51" s="2" t="inlineStr"/>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6530,7 +6646,7 @@
       <c r="U51" s="2" t="inlineStr"/>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
@@ -6579,22 +6695,22 @@
       <c r="B52" s="2" t="inlineStr"/>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>沪A65668D</t>
+          <t>沪A73927D</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6627,12 +6743,12 @@
       <c r="N52" s="2" t="inlineStr"/>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6646,7 +6762,7 @@
       <c r="U52" s="2" t="inlineStr"/>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
@@ -6695,22 +6811,22 @@
       <c r="B53" s="2" t="inlineStr"/>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>沪A09172D</t>
+          <t>沪A62981D</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -6748,7 +6864,7 @@
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6762,7 +6878,7 @@
       <c r="U53" s="2" t="inlineStr"/>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
@@ -6811,22 +6927,22 @@
       <c r="B54" s="2" t="inlineStr"/>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>沪A90275D</t>
+          <t>沪A68261D</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
@@ -6864,7 +6980,7 @@
       </c>
       <c r="P54" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q54" s="2" t="inlineStr">
@@ -6878,7 +6994,7 @@
       <c r="U54" s="2" t="inlineStr"/>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="W54" s="2" t="inlineStr">
@@ -6903,22 +7019,18 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC54" s="2" t="inlineStr">
-        <is>
-          <t>140.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr"/>
       <c r="AD54" s="2" t="inlineStr">
         <is>
-          <t>2/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -6931,22 +7043,22 @@
       <c r="B55" s="2" t="inlineStr"/>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>沪A05218D</t>
+          <t>沪A36993D</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>东高路张杨北路</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
           <t>康恩路康浦路</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6984,7 +7096,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -6998,7 +7110,7 @@
       <c r="U55" s="2" t="inlineStr"/>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W55" s="2" t="inlineStr">
@@ -7023,22 +7135,18 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>126.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr"/>
       <c r="AD55" s="2" t="inlineStr">
         <is>
-          <t>1/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
@@ -7051,22 +7159,22 @@
       <c r="B56" s="2" t="inlineStr"/>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>沪A66883D</t>
+          <t>沪A68895D</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>康恩路康浦路</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
           <t>东高路张杨北路</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
@@ -7099,12 +7207,12 @@
       <c r="N56" s="2" t="inlineStr"/>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -7118,7 +7226,7 @@
       <c r="U56" s="2" t="inlineStr"/>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
@@ -7143,84 +7251,76 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC56" s="2" t="inlineStr">
-        <is>
-          <t>153.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr"/>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/28</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr"/>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A02316D</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N57" s="2" t="inlineStr"/>
       <c r="O57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7228,7 +7328,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7242,7 +7342,7 @@
       <c r="U57" s="2" t="inlineStr"/>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
@@ -7252,65 +7352,61 @@
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC57" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr"/>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr"/>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A65668D</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
@@ -7348,7 +7444,7 @@
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -7362,7 +7458,7 @@
       <c r="U58" s="2" t="inlineStr"/>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
@@ -7387,7 +7483,7 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7398,77 +7494,73 @@
       <c r="AC58" s="2" t="inlineStr"/>
       <c r="AD58" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr"/>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A09172D</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>08:24</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>104分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N59" s="2" t="inlineStr"/>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7482,7 +7574,7 @@
       <c r="U59" s="2" t="inlineStr"/>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
@@ -7492,107 +7584,99 @@
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC59" s="2" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr"/>
       <c r="AD59" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr"/>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A90275D</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N60" s="2" t="inlineStr"/>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7606,7 +7690,7 @@
       <c r="U60" s="2" t="inlineStr"/>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>06:40</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
@@ -7616,17 +7700,17 @@
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7641,82 +7725,78 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>140.0</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>2/28</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr"/>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A05218D</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N61" s="2" t="inlineStr"/>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7730,7 +7810,7 @@
       <c r="U61" s="2" t="inlineStr"/>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
@@ -7740,17 +7820,17 @@
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7765,40 +7845,40 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>126.0</t>
         </is>
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>1/28</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr"/>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A66883D</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
@@ -7831,12 +7911,12 @@
       <c r="N62" s="2" t="inlineStr"/>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -7850,7 +7930,7 @@
       <c r="U62" s="2" t="inlineStr"/>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="W62" s="2" t="inlineStr">
@@ -7880,83 +7960,83 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC62" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr"/>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A67672D</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N63" s="2" t="inlineStr"/>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -7970,7 +8050,7 @@
       <c r="U63" s="2" t="inlineStr"/>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="W63" s="2" t="inlineStr">
@@ -7980,17 +8060,17 @@
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -8005,40 +8085,40 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>141.0</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>3/28</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr"/>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A72305D</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -8071,12 +8151,12 @@
       <c r="N64" s="2" t="inlineStr"/>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -8090,7 +8170,7 @@
       <c r="U64" s="2" t="inlineStr"/>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
@@ -8115,7 +8195,7 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
@@ -8126,35 +8206,35 @@
       <c r="AC64" s="2" t="inlineStr"/>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>—/28</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr"/>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>沪A61166D</t>
+          <t>沪A55102D</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
@@ -8187,12 +8267,12 @@
       <c r="N65" s="2" t="inlineStr"/>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:11</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8206,7 +8286,7 @@
       <c r="U65" s="2" t="inlineStr"/>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W65" s="2" t="inlineStr">
@@ -8231,46 +8311,50 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB65" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC65" s="2" t="inlineStr"/>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>151.0</t>
+        </is>
+      </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/28</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr"/>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A71572D</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -8303,12 +8387,12 @@
       <c r="N66" s="2" t="inlineStr"/>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8322,7 +8406,7 @@
       <c r="U66" s="2" t="inlineStr"/>
       <c r="V66" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="W66" s="2" t="inlineStr">
@@ -8347,46 +8431,50 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC66" s="2" t="inlineStr"/>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD66" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr"/>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A37823D</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -8419,12 +8507,12 @@
       <c r="N67" s="2" t="inlineStr"/>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:31</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8438,7 +8526,7 @@
       <c r="U67" s="2" t="inlineStr"/>
       <c r="V67" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W67" s="2" t="inlineStr">
@@ -8463,46 +8551,50 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>149.0</t>
+        </is>
+      </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/28</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr"/>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A70597D</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -8535,12 +8627,12 @@
       <c r="N68" s="2" t="inlineStr"/>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8554,7 +8646,7 @@
       <c r="U68" s="2" t="inlineStr"/>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
@@ -8579,46 +8671,50 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB68" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC68" s="2" t="inlineStr"/>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>163.0</t>
+        </is>
+      </c>
       <c r="AD68" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/28</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>浦东78路</t>
+          <t>浦东35路</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr"/>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A37267D</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
+          <t>康恩路康浦路</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>港城路地铁站</t>
+          <t>东高路张杨北路</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -8651,12 +8747,12 @@
       <c r="N69" s="2" t="inlineStr"/>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8670,7 +8766,7 @@
       <c r="U69" s="2" t="inlineStr"/>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>07:32</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
@@ -8695,18 +8791,22 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC69" s="2" t="inlineStr"/>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>147.0</t>
+        </is>
+      </c>
       <c r="AD69" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/28</t>
         </is>
       </c>
     </row>
@@ -8719,7 +8819,7 @@
       <c r="B70" s="2" t="inlineStr"/>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>沪A53629D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -8729,7 +8829,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -8739,40 +8839,44 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:34</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q70" s="2" t="inlineStr">
@@ -8786,7 +8890,7 @@
       <c r="U70" s="2" t="inlineStr"/>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>07:42</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
@@ -8796,33 +8900,37 @@
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB70" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC70" s="2" t="inlineStr"/>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8835,22 +8943,22 @@
       <c r="B71" s="2" t="inlineStr"/>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>06:25</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>07:47</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -8888,7 +8996,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8902,7 +9010,7 @@
       <c r="U71" s="2" t="inlineStr"/>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>07:47</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
@@ -8927,7 +9035,7 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
@@ -8951,7 +9059,7 @@
       <c r="B72" s="2" t="inlineStr"/>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -8961,7 +9069,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8971,40 +9079,44 @@
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:24</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -9018,7 +9130,7 @@
       <c r="U72" s="2" t="inlineStr"/>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>07:54</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
@@ -9028,33 +9140,37 @@
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC72" s="2" t="inlineStr"/>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9067,7 +9183,7 @@
       <c r="B73" s="2" t="inlineStr"/>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -9077,7 +9193,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9087,40 +9203,44 @@
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:06</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -9134,7 +9254,7 @@
       <c r="U73" s="2" t="inlineStr"/>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
@@ -9144,17 +9264,17 @@
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9169,12 +9289,12 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AD73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9187,60 +9307,64 @@
       <c r="B74" s="2" t="inlineStr"/>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>08:06</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9254,7 +9378,7 @@
       <c r="U74" s="2" t="inlineStr"/>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>08:06</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
@@ -9264,33 +9388,37 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC74" s="2" t="inlineStr"/>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9303,7 +9431,7 @@
       <c r="B75" s="2" t="inlineStr"/>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -9313,7 +9441,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -9351,12 +9479,12 @@
       <c r="N75" s="2" t="inlineStr"/>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -9370,7 +9498,7 @@
       <c r="U75" s="2" t="inlineStr"/>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>08:18</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
@@ -9400,17 +9528,13 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC75" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr"/>
       <c r="AD75" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9547,7 @@
       <c r="B76" s="2" t="inlineStr"/>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -9433,7 +9557,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -9443,40 +9567,44 @@
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q76" s="2" t="inlineStr">
@@ -9490,7 +9618,7 @@
       <c r="U76" s="2" t="inlineStr"/>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
@@ -9500,17 +9628,17 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9520,13 +9648,17 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC76" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9671,7 @@
       <c r="B77" s="2" t="inlineStr"/>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -9549,7 +9681,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -9559,32 +9691,36 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:46</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9592,7 +9728,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9606,7 +9742,7 @@
       <c r="U77" s="2" t="inlineStr"/>
       <c r="V77" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="W77" s="2" t="inlineStr">
@@ -9616,17 +9752,17 @@
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA77" s="2" t="inlineStr">
@@ -9641,12 +9777,12 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9659,60 +9795,64 @@
       <c r="B78" s="2" t="inlineStr"/>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:04</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -9726,7 +9866,7 @@
       <c r="U78" s="2" t="inlineStr"/>
       <c r="V78" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>07:10</t>
         </is>
       </c>
       <c r="W78" s="2" t="inlineStr">
@@ -9736,17 +9876,17 @@
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9761,12 +9901,12 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9779,7 +9919,7 @@
       <c r="B79" s="2" t="inlineStr"/>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -9789,7 +9929,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -9799,40 +9939,44 @@
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9846,7 +9990,7 @@
       <c r="U79" s="2" t="inlineStr"/>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>07:15</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
@@ -9856,33 +10000,37 @@
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB79" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AC79" s="2" t="inlineStr"/>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9895,7 +10043,7 @@
       <c r="B80" s="2" t="inlineStr"/>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -9905,7 +10053,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -9943,12 +10091,12 @@
       <c r="N80" s="2" t="inlineStr"/>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9962,7 +10110,7 @@
       <c r="U80" s="2" t="inlineStr"/>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
@@ -9992,17 +10140,13 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC80" s="2" t="inlineStr">
-        <is>
-          <t>90.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr"/>
       <c r="AD80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -10015,22 +10159,22 @@
       <c r="B81" s="2" t="inlineStr"/>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
@@ -10063,12 +10207,12 @@
       <c r="N81" s="2" t="inlineStr"/>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="Q81" s="2" t="inlineStr">
@@ -10082,7 +10226,7 @@
       <c r="U81" s="2" t="inlineStr"/>
       <c r="V81" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="W81" s="2" t="inlineStr">
@@ -10119,6 +10263,2754 @@
       <c r="AD81" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr"/>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr">
+        <is>
+          <t>96分钟</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr"/>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>07:32</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD82" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr"/>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>09:21</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr">
+        <is>
+          <t>99分钟</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr"/>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AD83" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr"/>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr">
+        <is>
+          <t>95分钟</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr"/>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>07:47</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD84" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr"/>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>全程车</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr">
+        <is>
+          <t>97分钟</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr"/>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>终点ETA确认/一致估算</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD85" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr"/>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N86" s="2" t="inlineStr"/>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr"/>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AD86" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr"/>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N87" s="2" t="inlineStr"/>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr"/>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr"/>
+      <c r="AD87" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr"/>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N88" s="2" t="inlineStr"/>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr"/>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AD88" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr"/>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N89" s="2" t="inlineStr"/>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr"/>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr"/>
+      <c r="AD89" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr"/>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N90" s="2" t="inlineStr"/>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr"/>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD90" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr"/>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr"/>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr"/>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD91" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr"/>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr"/>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr"/>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr"/>
+      <c r="AD92" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr"/>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr"/>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr"/>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AD93" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr"/>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr"/>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr"/>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr"/>
+      <c r="AD94" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr"/>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr"/>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr"/>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>106.0</t>
+        </is>
+      </c>
+      <c r="AD95" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr"/>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr"/>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr"/>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AD96" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr"/>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr"/>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr"/>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AD97" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr"/>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N98" s="2" t="inlineStr"/>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr"/>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AD98" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr"/>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N99" s="2" t="inlineStr"/>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr"/>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr"/>
+      <c r="AD99" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr"/>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N100" s="2" t="inlineStr"/>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr"/>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr"/>
+      <c r="AD100" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr"/>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N101" s="2" t="inlineStr"/>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr"/>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>09:40</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AD101" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr"/>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N102" s="2" t="inlineStr"/>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr"/>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AD102" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr"/>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N103" s="2" t="inlineStr"/>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr"/>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr"/>
+      <c r="AD103" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>浦东78路</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr"/>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="N104" s="2" t="inlineStr"/>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr"/>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AD104" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-operations.xlsx
+++ b/data/export/2026-10-15-operations.xlsx
@@ -680,7 +680,7 @@
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
@@ -724,17 +724,17 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -928,7 +928,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD4" s="2" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="AD5" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="AD8" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -1792,7 +1792,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD11" s="2" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -2080,17 +2080,17 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="AD15" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD16" s="2" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AD18" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3068,17 +3068,17 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AD22" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD24" s="2" t="inlineStr">
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3812,17 +3812,17 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="AD29" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD30" s="2" t="inlineStr">
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
       </c>
       <c r="AD32" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4804,17 +4804,17 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
       </c>
       <c r="AD36" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD37" s="2" t="inlineStr">
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -5504,7 +5504,7 @@
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5548,12 +5548,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD41" s="2" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="AD42" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -5806,7 +5806,7 @@
       </c>
       <c r="AD43" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6044,17 +6044,17 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="AD50" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="AD53" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="P55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q55" s="2" t="inlineStr">
@@ -7289,7 +7289,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD55" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7488,7 @@
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -7532,17 +7532,17 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD60" s="2" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="AD61" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8152,17 +8152,17 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q63" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD63" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="AD64" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -8524,17 +8524,17 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -9268,12 +9268,12 @@
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD71" s="2" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="AD72" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9640,17 +9640,17 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AD76" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>7/15</t>
         </is>
       </c>
     </row>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="AD77" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10260,17 +10260,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10340,7 +10340,7 @@
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD80" s="2" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="P83" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q83" s="2" t="inlineStr">
@@ -10756,17 +10756,17 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10890,7 +10890,7 @@
       </c>
       <c r="AD84" s="2" t="inlineStr">
         <is>
-          <t>7/15</t>
+          <t>8/15</t>
         </is>
       </c>
     </row>
@@ -10960,7 +10960,7 @@
       </c>
       <c r="P85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q85" s="2" t="inlineStr">
@@ -11004,12 +11004,12 @@
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD85" s="2" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11372,17 +11372,17 @@
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11506,7 +11506,7 @@
       </c>
       <c r="AD89" s="2" t="inlineStr">
         <is>
-          <t>8/15</t>
+          <t>9/15</t>
         </is>
       </c>
     </row>
@@ -11549,12 +11549,12 @@
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr"/>
@@ -11576,7 +11576,7 @@
       </c>
       <c r="P90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="Q90" s="2" t="inlineStr">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AD90" s="2" t="inlineStr">
@@ -11663,32 +11663,36 @@
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -11696,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11720,17 +11724,17 @@
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11740,12 +11744,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11783,32 +11787,36 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -11816,7 +11824,7 @@
       </c>
       <c r="P92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:52</t>
         </is>
       </c>
       <c r="Q92" s="2" t="inlineStr">
@@ -11840,17 +11848,17 @@
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
@@ -11860,17 +11868,17 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11903,32 +11911,36 @@
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>66分钟</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -11936,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11960,17 +11972,17 @@
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11980,17 +11992,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -12023,32 +12035,36 @@
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
           <t>06:02</t>
@@ -12056,7 +12072,7 @@
       </c>
       <c r="P94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="Q94" s="2" t="inlineStr">
@@ -12080,17 +12096,17 @@
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -12100,12 +12116,12 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AD94" s="2" t="inlineStr">
@@ -12143,32 +12159,36 @@
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -12176,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12200,17 +12220,17 @@
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA95" s="2" t="inlineStr">
@@ -12220,17 +12240,17 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>75.1</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -12296,7 +12316,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12340,12 +12360,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>73.8</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12416,7 +12436,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:22</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,17 +12480,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>76.6</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>9/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -12540,7 +12560,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -13168,7 +13188,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13222,7 +13242,7 @@
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -13470,7 +13490,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -13664,7 +13684,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13718,7 +13738,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13808,7 @@
       </c>
       <c r="P108" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q108" s="2" t="inlineStr">
@@ -13832,17 +13852,17 @@
       </c>
       <c r="AB108" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC108" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14192,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14216,17 +14236,17 @@
       </c>
       <c r="AB111" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14292,7 +14312,7 @@
       </c>
       <c r="P112" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q112" s="2" t="inlineStr">
@@ -14358,7 +14378,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14502,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14796,7 +14816,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14840,17 +14860,17 @@
       </c>
       <c r="AB116" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -14916,7 +14936,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15040,7 +15060,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15094,7 +15114,7 @@
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15164,7 +15184,7 @@
       </c>
       <c r="P119" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q119" s="2" t="inlineStr">
@@ -15213,12 +15233,12 @@
       </c>
       <c r="AC119" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15308,7 @@
       </c>
       <c r="P120" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q120" s="2" t="inlineStr">
@@ -15332,17 +15352,17 @@
       </c>
       <c r="AB120" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC120" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -15466,7 +15486,7 @@
       </c>
       <c r="AD121" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -15536,7 +15556,7 @@
       </c>
       <c r="P122" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q122" s="2" t="inlineStr">
@@ -15590,7 +15610,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -15656,7 +15676,7 @@
       </c>
       <c r="P123" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q123" s="2" t="inlineStr">
@@ -15700,17 +15720,17 @@
       </c>
       <c r="AB123" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC123" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15924,7 @@
       </c>
       <c r="P125" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q125" s="2" t="inlineStr">
@@ -16148,7 +16168,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16652,7 +16672,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16706,7 +16726,7 @@
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -16954,7 +16974,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -17148,7 +17168,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17202,7 +17222,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -17272,7 +17292,7 @@
       </c>
       <c r="P136" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q136" s="2" t="inlineStr">
@@ -17316,17 +17336,17 @@
       </c>
       <c r="AB136" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC136" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -17396,7 +17416,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17440,17 +17460,17 @@
       </c>
       <c r="AB137" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -17698,7 +17718,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17892,7 +17912,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17936,17 +17956,17 @@
       </c>
       <c r="AB141" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -18140,7 +18160,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18264,7 +18284,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18318,7 +18338,7 @@
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -18388,7 +18408,7 @@
       </c>
       <c r="P145" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q145" s="2" t="inlineStr">
@@ -18437,12 +18457,12 @@
       </c>
       <c r="AC145" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -18512,7 +18532,7 @@
       </c>
       <c r="P146" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q146" s="2" t="inlineStr">
@@ -18566,7 +18586,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18780,7 @@
       </c>
       <c r="P148" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q148" s="2" t="inlineStr">
@@ -19310,7 +19330,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19648,7 @@
       </c>
       <c r="P155" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q155" s="2" t="inlineStr">
@@ -19682,7 +19702,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -19930,7 +19950,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -20000,7 +20020,7 @@
       </c>
       <c r="P158" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q158" s="2" t="inlineStr">
@@ -20049,12 +20069,12 @@
       </c>
       <c r="AC158" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -20124,7 +20144,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20178,7 +20198,7 @@
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20446,7 @@
       </c>
       <c r="AD161" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -21248,7 +21268,7 @@
       </c>
       <c r="P168" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q168" s="2" t="inlineStr">
@@ -21292,17 +21312,17 @@
       </c>
       <c r="AB168" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC168" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -21368,7 +21388,7 @@
       </c>
       <c r="P169" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q169" s="2" t="inlineStr">
@@ -21488,7 +21508,7 @@
       </c>
       <c r="P170" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q170" s="2" t="inlineStr">
@@ -21532,17 +21552,17 @@
       </c>
       <c r="AB170" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC170" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -21612,7 +21632,7 @@
       </c>
       <c r="P171" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q171" s="2" t="inlineStr">
@@ -21656,17 +21676,17 @@
       </c>
       <c r="AB171" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC171" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21736,7 +21756,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21780,17 +21800,17 @@
       </c>
       <c r="AB172" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -21860,7 +21880,7 @@
       </c>
       <c r="P173" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q173" s="2" t="inlineStr">
@@ -21914,7 +21934,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -21984,7 +22004,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22028,17 +22048,17 @@
       </c>
       <c r="AB174" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22108,7 +22128,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22232,7 +22252,7 @@
       </c>
       <c r="P176" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q176" s="2" t="inlineStr">
@@ -22286,7 +22306,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -22356,7 +22376,7 @@
       </c>
       <c r="P177" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q177" s="2" t="inlineStr">
@@ -22480,7 +22500,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22534,7 +22554,7 @@
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -22604,7 +22624,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22658,7 +22678,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -22906,7 +22926,7 @@
       </c>
       <c r="AD181" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>27/30</t>
         </is>
       </c>
     </row>
@@ -23030,7 +23050,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>21/30</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23736,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23813,12 +23833,12 @@
       </c>
       <c r="I189" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="J189" s="2" t="inlineStr">
         <is>
-          <t>143分钟</t>
+          <t>144分钟</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr"/>
@@ -23840,7 +23860,7 @@
       </c>
       <c r="P189" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q189" s="2" t="inlineStr">
@@ -23889,12 +23909,12 @@
       </c>
       <c r="AC189" s="2" t="inlineStr">
         <is>
-          <t>138.2</t>
+          <t>138.5</t>
         </is>
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>9/30</t>
+          <t>10/30</t>
         </is>
       </c>
     </row>
@@ -23960,7 +23980,7 @@
       </c>
       <c r="P190" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q190" s="2" t="inlineStr">
@@ -24043,32 +24063,36 @@
       </c>
       <c r="G191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="J191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>129分钟</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
       <c r="M191" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N191" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N191" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24076,7 +24100,7 @@
       </c>
       <c r="P191" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="Q191" s="2" t="inlineStr">
@@ -24100,17 +24124,17 @@
       </c>
       <c r="X191" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y191" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z191" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA191" s="2" t="inlineStr">
@@ -24120,17 +24144,17 @@
       </c>
       <c r="AB191" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC191" s="2" t="inlineStr">
         <is>
-          <t>148.5</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>24/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -24163,32 +24187,36 @@
       </c>
       <c r="G192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="J192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>127分钟</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
       <c r="M192" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N192" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N192" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -24196,7 +24224,7 @@
       </c>
       <c r="P192" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q192" s="2" t="inlineStr">
@@ -24220,17 +24248,17 @@
       </c>
       <c r="X192" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y192" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z192" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA192" s="2" t="inlineStr">
@@ -24240,17 +24268,17 @@
       </c>
       <c r="AB192" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC192" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>140.5</t>
         </is>
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -24283,12 +24311,12 @@
       </c>
       <c r="G193" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq28推进至seq64，推进36站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I193" s="2" t="inlineStr">
@@ -24316,7 +24344,7 @@
       </c>
       <c r="P193" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q193" s="2" t="inlineStr">
@@ -24324,10 +24352,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R193" s="2" t="inlineStr"/>
-      <c r="S193" s="2" t="inlineStr"/>
+      <c r="R193" s="2" t="inlineStr">
+        <is>
+          <t>物理seq26（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S193" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
       <c r="T193" s="2" t="inlineStr"/>
-      <c r="U193" s="2" t="inlineStr"/>
+      <c r="U193" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq26映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="V193" s="2" t="inlineStr">
         <is>
           <t>19:10</t>
@@ -24370,7 +24410,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -24403,32 +24443,36 @@
       </c>
       <c r="G194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="J194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>128分钟</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
       <c r="M194" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N194" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N194" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24436,7 +24480,7 @@
       </c>
       <c r="P194" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q194" s="2" t="inlineStr">
@@ -24460,17 +24504,17 @@
       </c>
       <c r="X194" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y194" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z194" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA194" s="2" t="inlineStr">
@@ -24480,17 +24524,17 @@
       </c>
       <c r="AB194" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AC194" s="2" t="inlineStr">
         <is>
-          <t>162.0</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>27/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24523,32 +24567,36 @@
       </c>
       <c r="G195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:35</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>135分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N195" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N195" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -24556,7 +24604,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24580,17 +24628,17 @@
       </c>
       <c r="X195" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y195" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z195" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA195" s="2" t="inlineStr">
@@ -24600,17 +24648,17 @@
       </c>
       <c r="AB195" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>148.3</t>
+          <t>145.0</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>23/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24643,12 +24691,12 @@
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq28推进至seq47，推进19站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
@@ -24676,7 +24724,7 @@
       </c>
       <c r="P196" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="Q196" s="2" t="inlineStr">
@@ -24684,10 +24732,26 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="R196" s="2" t="inlineStr"/>
-      <c r="S196" s="2" t="inlineStr"/>
-      <c r="T196" s="2" t="inlineStr"/>
-      <c r="U196" s="2" t="inlineStr"/>
+      <c r="R196" s="2" t="inlineStr">
+        <is>
+          <t>物理seq31（站名待映射）</t>
+        </is>
+      </c>
+      <c r="S196" s="2" t="inlineStr">
+        <is>
+          <t>20:23</t>
+        </is>
+      </c>
+      <c r="T196" s="2" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="U196" s="2" t="inlineStr">
+        <is>
+          <t>折返点按重建物理位置seq31映射；到达按末次同向ETA估算；折返发车结合首次反向物理观测取区间中点，约±9分钟；反向位置物理seq28（站名待映射） ETA 0分钟参与校验</t>
+        </is>
+      </c>
       <c r="V196" s="2" t="inlineStr">
         <is>
           <t>19:30</t>
@@ -24796,7 +24860,7 @@
       </c>
       <c r="P197" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="Q197" s="2" t="inlineStr">
@@ -24850,7 +24914,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24916,7 +24980,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25003,32 +25067,36 @@
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>131分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N199" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N199" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -25036,7 +25104,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25060,17 +25128,17 @@
       </c>
       <c r="X199" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y199" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z199" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA199" s="2" t="inlineStr">
@@ -25080,17 +25148,17 @@
       </c>
       <c r="AB199" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>147.0</t>
+          <t>143.0</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25156,7 +25224,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25210,7 +25278,7 @@
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -25276,7 +25344,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25330,7 +25398,7 @@
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25464,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25450,7 +25518,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -25516,7 +25584,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -25640,7 +25708,7 @@
       </c>
       <c r="P204" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q204" s="2" t="inlineStr">
@@ -25684,12 +25752,12 @@
       </c>
       <c r="AB204" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC204" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD204" s="2" t="inlineStr">
@@ -25814,7 +25882,7 @@
       </c>
       <c r="AD205" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -25938,7 +26006,7 @@
       </c>
       <c r="AD206" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -26062,7 +26130,7 @@
       </c>
       <c r="AD207" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -26132,7 +26200,7 @@
       </c>
       <c r="P208" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q208" s="2" t="inlineStr">
@@ -26252,7 +26320,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26296,17 +26364,17 @@
       </c>
       <c r="AB209" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -26430,7 +26498,7 @@
       </c>
       <c r="AD210" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -26554,7 +26622,7 @@
       </c>
       <c r="AD211" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -26624,7 +26692,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26748,7 +26816,7 @@
       </c>
       <c r="P213" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q213" s="2" t="inlineStr">
@@ -26792,17 +26860,17 @@
       </c>
       <c r="AB213" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC213" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD213" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -27166,7 +27234,7 @@
       </c>
       <c r="AD216" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -27290,7 +27358,7 @@
       </c>
       <c r="AD217" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -27414,7 +27482,7 @@
       </c>
       <c r="AD218" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -27484,7 +27552,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -27528,17 +27596,17 @@
       </c>
       <c r="AB219" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC219" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD219" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -27608,7 +27676,7 @@
       </c>
       <c r="P220" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q220" s="2" t="inlineStr">
@@ -27652,12 +27720,12 @@
       </c>
       <c r="AB220" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC220" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD220" s="2" t="inlineStr">
@@ -27786,7 +27854,7 @@
       </c>
       <c r="AD221" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -27910,7 +27978,7 @@
       </c>
       <c r="AD222" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -28034,7 +28102,7 @@
       </c>
       <c r="AD223" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -28104,7 +28172,7 @@
       </c>
       <c r="P224" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q224" s="2" t="inlineStr">
@@ -28282,7 +28350,7 @@
       </c>
       <c r="AD225" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -28522,7 +28590,7 @@
       </c>
       <c r="AD227" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -28588,7 +28656,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28632,17 +28700,17 @@
       </c>
       <c r="AB228" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -28762,7 +28830,7 @@
       </c>
       <c r="AD229" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -28832,7 +28900,7 @@
       </c>
       <c r="P230" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q230" s="2" t="inlineStr">
@@ -28876,17 +28944,17 @@
       </c>
       <c r="AB230" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC230" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD230" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -28956,7 +29024,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29134,7 +29202,7 @@
       </c>
       <c r="AD232" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -29502,7 +29570,7 @@
       </c>
       <c r="AD235" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -29568,7 +29636,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -29612,17 +29680,17 @@
       </c>
       <c r="AB236" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC236" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD236" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -29746,7 +29814,7 @@
       </c>
       <c r="AD237" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -29870,7 +29938,7 @@
       </c>
       <c r="AD238" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -29994,7 +30062,7 @@
       </c>
       <c r="AD239" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -30060,7 +30128,7 @@
       </c>
       <c r="P240" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q240" s="2" t="inlineStr">
@@ -30250,7 +30318,7 @@
       </c>
       <c r="AD241" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -30316,7 +30384,7 @@
       </c>
       <c r="P242" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q242" s="2" t="inlineStr">
@@ -30372,17 +30440,17 @@
       </c>
       <c r="AB242" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC242" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD242" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -30506,7 +30574,7 @@
       </c>
       <c r="AD243" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -30630,7 +30698,7 @@
       </c>
       <c r="AD244" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -30878,7 +30946,7 @@
       </c>
       <c r="AD246" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -31126,7 +31194,7 @@
       </c>
       <c r="AD248" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -31250,7 +31318,7 @@
       </c>
       <c r="AD249" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -31374,7 +31442,7 @@
       </c>
       <c r="AD250" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -31498,7 +31566,7 @@
       </c>
       <c r="AD251" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -31622,7 +31690,7 @@
       </c>
       <c r="AD252" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -31746,7 +31814,7 @@
       </c>
       <c r="AD253" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -31994,7 +32062,7 @@
       </c>
       <c r="AD255" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -32242,7 +32310,7 @@
       </c>
       <c r="AD257" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -32366,7 +32434,7 @@
       </c>
       <c r="AD258" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -32490,7 +32558,7 @@
       </c>
       <c r="AD259" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -32614,7 +32682,7 @@
       </c>
       <c r="AD260" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32752,7 @@
       </c>
       <c r="P261" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q261" s="2" t="inlineStr">
@@ -32728,12 +32796,12 @@
       </c>
       <c r="AB261" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC261" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD261" s="2" t="inlineStr">
@@ -32862,7 +32930,7 @@
       </c>
       <c r="AD262" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -32986,7 +33054,7 @@
       </c>
       <c r="AD263" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -33234,7 +33302,7 @@
       </c>
       <c r="AD265" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -33300,7 +33368,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33344,17 +33412,17 @@
       </c>
       <c r="AB266" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -33478,7 +33546,7 @@
       </c>
       <c r="AD267" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -33548,7 +33616,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33726,7 +33794,7 @@
       </c>
       <c r="AD269" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -33916,7 +33984,7 @@
       </c>
       <c r="P271" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q271" s="2" t="inlineStr">
@@ -34040,7 +34108,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -34084,17 +34152,17 @@
       </c>
       <c r="AB272" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC272" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD272" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -34218,7 +34286,7 @@
       </c>
       <c r="AD273" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -34342,7 +34410,7 @@
       </c>
       <c r="AD274" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -34412,7 +34480,7 @@
       </c>
       <c r="P275" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q275" s="2" t="inlineStr">
@@ -34456,17 +34524,17 @@
       </c>
       <c r="AB275" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC275" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD275" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -34590,7 +34658,7 @@
       </c>
       <c r="AD276" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -34714,7 +34782,7 @@
       </c>
       <c r="AD277" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -34784,7 +34852,7 @@
       </c>
       <c r="P278" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q278" s="2" t="inlineStr">
@@ -34828,12 +34896,12 @@
       </c>
       <c r="AB278" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC278" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD278" s="2" t="inlineStr">
@@ -34962,7 +35030,7 @@
       </c>
       <c r="AD279" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -35086,7 +35154,7 @@
       </c>
       <c r="AD280" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -35206,7 +35274,7 @@
       </c>
       <c r="AD281" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -35454,7 +35522,7 @@
       </c>
       <c r="AD283" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -35524,7 +35592,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35568,17 +35636,17 @@
       </c>
       <c r="AB284" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -35648,7 +35716,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35826,7 +35894,7 @@
       </c>
       <c r="AD286" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -36016,7 +36084,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36060,17 +36128,17 @@
       </c>
       <c r="AB288" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC288" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD288" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -36140,7 +36208,7 @@
       </c>
       <c r="P289" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q289" s="2" t="inlineStr">
@@ -36318,7 +36386,7 @@
       </c>
       <c r="AD290" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -36442,7 +36510,7 @@
       </c>
       <c r="AD291" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -36566,7 +36634,7 @@
       </c>
       <c r="AD292" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -36636,7 +36704,7 @@
       </c>
       <c r="P293" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q293" s="2" t="inlineStr">
@@ -36680,17 +36748,17 @@
       </c>
       <c r="AB293" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC293" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD293" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -36814,7 +36882,7 @@
       </c>
       <c r="AD294" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -36938,7 +37006,7 @@
       </c>
       <c r="AD295" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -37008,7 +37076,7 @@
       </c>
       <c r="P296" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q296" s="2" t="inlineStr">
@@ -37052,12 +37120,12 @@
       </c>
       <c r="AB296" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC296" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD296" s="2" t="inlineStr">
@@ -37182,7 +37250,7 @@
       </c>
       <c r="AD297" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -37430,7 +37498,7 @@
       </c>
       <c r="AD299" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -37500,7 +37568,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37544,17 +37612,17 @@
       </c>
       <c r="AB300" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -37624,7 +37692,7 @@
       </c>
       <c r="P301" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="Q301" s="2" t="inlineStr">
@@ -37748,7 +37816,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37835,32 +37903,36 @@
       </c>
       <c r="G303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H303" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="J303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K303" s="2" t="inlineStr"/>
       <c r="L303" s="2" t="inlineStr"/>
       <c r="M303" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N303" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N303" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O303" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -37868,7 +37940,7 @@
       </c>
       <c r="P303" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="Q303" s="2" t="inlineStr">
@@ -37892,17 +37964,17 @@
       </c>
       <c r="X303" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y303" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z303" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA303" s="2" t="inlineStr">
@@ -37912,17 +37984,17 @@
       </c>
       <c r="AB303" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AC303" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD303" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -37955,32 +38027,36 @@
       </c>
       <c r="G304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H304" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:18</t>
         </is>
       </c>
       <c r="J304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K304" s="2" t="inlineStr"/>
       <c r="L304" s="2" t="inlineStr"/>
       <c r="M304" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N304" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N304" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O304" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -37988,7 +38064,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38012,17 +38088,17 @@
       </c>
       <c r="X304" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y304" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z304" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA304" s="2" t="inlineStr">
@@ -38032,17 +38108,17 @@
       </c>
       <c r="AB304" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC304" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD304" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -38075,32 +38151,36 @@
       </c>
       <c r="G305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H305" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:34</t>
         </is>
       </c>
       <c r="J305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="K305" s="2" t="inlineStr"/>
       <c r="L305" s="2" t="inlineStr"/>
       <c r="M305" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N305" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N305" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O305" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -38108,7 +38188,7 @@
       </c>
       <c r="P305" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q305" s="2" t="inlineStr">
@@ -38132,17 +38212,17 @@
       </c>
       <c r="X305" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y305" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z305" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA305" s="2" t="inlineStr">
@@ -38152,12 +38232,12 @@
       </c>
       <c r="AB305" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC305" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AD305" s="2" t="inlineStr">
@@ -38195,32 +38275,36 @@
       </c>
       <c r="G306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H306" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
       <c r="L306" s="2" t="inlineStr"/>
       <c r="M306" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N306" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N306" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O306" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -38228,7 +38312,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38252,17 +38336,17 @@
       </c>
       <c r="X306" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y306" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z306" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA306" s="2" t="inlineStr">
@@ -38272,17 +38356,17 @@
       </c>
       <c r="AB306" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -38348,7 +38432,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38468,7 +38552,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
@@ -38512,17 +38596,17 @@
       </c>
       <c r="AB308" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AC308" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AD308" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-15-operations.xlsx
+++ b/data/export/2026-10-15-operations.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AD2" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="AD3" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD7" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD10" s="2" t="inlineStr">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="AD13" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -2204,17 +2204,17 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD14" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AD17" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3024,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD21" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD25" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="AD27" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -3892,7 +3892,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3936,17 +3936,17 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD28" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4318,7 @@
       </c>
       <c r="AD31" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4809,12 +4809,12 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD35" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5132,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD38" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="AD39" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -5380,7 +5380,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -5424,17 +5424,17 @@
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD40" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6000,7 +6000,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD45" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -6124,7 +6124,7 @@
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -6168,12 +6168,12 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD46" s="2" t="inlineStr">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -6416,17 +6416,17 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD48" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AD49" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AD56" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -7542,7 +7542,7 @@
       </c>
       <c r="AD57" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8108,7 +8108,7 @@
       </c>
       <c r="P62" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q62" s="2" t="inlineStr">
@@ -8157,12 +8157,12 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD62" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="AD65" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -8648,12 +8648,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD66" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -8772,17 +8772,17 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD67" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -9154,7 +9154,7 @@
       </c>
       <c r="AD70" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -9596,7 +9596,7 @@
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD74" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -10092,7 +10092,7 @@
       </c>
       <c r="P78" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q78" s="2" t="inlineStr">
@@ -10136,12 +10136,12 @@
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD78" s="2" t="inlineStr">
@@ -10216,7 +10216,7 @@
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -10260,17 +10260,17 @@
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD79" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AD82" s="2" t="inlineStr">
         <is>
-          <t>5/15</t>
+          <t>6/15</t>
         </is>
       </c>
     </row>
@@ -10766,7 +10766,7 @@
       </c>
       <c r="AD83" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="P88" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q88" s="2" t="inlineStr">
@@ -11377,12 +11377,12 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD88" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -11700,7 +11700,7 @@
       </c>
       <c r="P91" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q91" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD91" s="2" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AD92" s="2" t="inlineStr">
         <is>
-          <t>3/15</t>
+          <t>4/15</t>
         </is>
       </c>
     </row>
@@ -11948,7 +11948,7 @@
       </c>
       <c r="P93" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q93" s="2" t="inlineStr">
@@ -11992,17 +11992,17 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD93" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12169,24 +12169,24 @@
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>21:48</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O95" s="2" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="P95" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:32</t>
         </is>
       </c>
       <c r="Q95" s="2" t="inlineStr">
@@ -12245,12 +12245,12 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AD95" s="2" t="inlineStr">
         <is>
-          <t>4/15</t>
+          <t>3/15</t>
         </is>
       </c>
     </row>
@@ -12283,32 +12283,36 @@
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
           <t>06:42</t>
@@ -12316,7 +12320,7 @@
       </c>
       <c r="P96" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q96" s="2" t="inlineStr">
@@ -12340,17 +12344,17 @@
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
@@ -12360,12 +12364,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>73.8</t>
+          <t>74.0</t>
         </is>
       </c>
       <c r="AD96" s="2" t="inlineStr">
@@ -12403,32 +12407,36 @@
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:24</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
           <t>07:02</t>
@@ -12436,7 +12444,7 @@
       </c>
       <c r="P97" s="2" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="Q97" s="2" t="inlineStr">
@@ -12460,17 +12468,17 @@
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA97" s="2" t="inlineStr">
@@ -12480,17 +12488,17 @@
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>76.6</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AD97" s="2" t="inlineStr">
         <is>
-          <t>6/15</t>
+          <t>5/15</t>
         </is>
       </c>
     </row>
@@ -12560,7 +12568,7 @@
       </c>
       <c r="P98" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q98" s="2" t="inlineStr">
@@ -12604,17 +12612,17 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD98" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -12738,7 +12746,7 @@
       </c>
       <c r="AD99" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -12986,7 +12994,7 @@
       </c>
       <c r="AD101" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13196,7 @@
       </c>
       <c r="P103" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q103" s="2" t="inlineStr">
@@ -13232,17 +13240,17 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD103" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -13366,7 +13374,7 @@
       </c>
       <c r="AD104" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13498,7 @@
       </c>
       <c r="AD105" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -13684,7 +13692,7 @@
       </c>
       <c r="P107" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q107" s="2" t="inlineStr">
@@ -13738,7 +13746,7 @@
       </c>
       <c r="AD107" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -13862,7 +13870,7 @@
       </c>
       <c r="AD108" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -14122,7 +14130,7 @@
       </c>
       <c r="AD110" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -14192,7 +14200,7 @@
       </c>
       <c r="P111" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q111" s="2" t="inlineStr">
@@ -14241,12 +14249,12 @@
       </c>
       <c r="AC111" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD111" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -14378,7 +14386,7 @@
       </c>
       <c r="AD112" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14510,7 @@
       </c>
       <c r="AD113" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -14746,7 +14754,7 @@
       </c>
       <c r="AD115" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14824,7 @@
       </c>
       <c r="P116" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q116" s="2" t="inlineStr">
@@ -14865,12 +14873,12 @@
       </c>
       <c r="AC116" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD116" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -14936,7 +14944,7 @@
       </c>
       <c r="P117" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q117" s="2" t="inlineStr">
@@ -15060,7 +15068,7 @@
       </c>
       <c r="P118" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q118" s="2" t="inlineStr">
@@ -15104,17 +15112,17 @@
       </c>
       <c r="AB118" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC118" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD118" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -15238,7 +15246,7 @@
       </c>
       <c r="AD119" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -15362,7 +15370,7 @@
       </c>
       <c r="AD120" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15618,7 @@
       </c>
       <c r="AD122" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -15730,7 +15738,7 @@
       </c>
       <c r="AD123" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16106,7 @@
       </c>
       <c r="AD126" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -16168,7 +16176,7 @@
       </c>
       <c r="P127" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q127" s="2" t="inlineStr">
@@ -16212,17 +16220,17 @@
       </c>
       <c r="AB127" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC127" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD127" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16354,7 @@
       </c>
       <c r="AD128" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -16672,7 +16680,7 @@
       </c>
       <c r="P131" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q131" s="2" t="inlineStr">
@@ -16716,17 +16724,17 @@
       </c>
       <c r="AB131" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC131" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD131" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -16850,7 +16858,7 @@
       </c>
       <c r="AD132" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -16974,7 +16982,7 @@
       </c>
       <c r="AD133" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -17168,7 +17176,7 @@
       </c>
       <c r="P135" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q135" s="2" t="inlineStr">
@@ -17222,7 +17230,7 @@
       </c>
       <c r="AD135" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -17346,7 +17354,7 @@
       </c>
       <c r="AD136" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -17416,7 +17424,7 @@
       </c>
       <c r="P137" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q137" s="2" t="inlineStr">
@@ -17465,12 +17473,12 @@
       </c>
       <c r="AC137" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD137" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -17594,7 +17602,7 @@
       </c>
       <c r="AD138" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -17718,7 +17726,7 @@
       </c>
       <c r="AD139" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -17912,7 +17920,7 @@
       </c>
       <c r="P141" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q141" s="2" t="inlineStr">
@@ -17961,12 +17969,12 @@
       </c>
       <c r="AC141" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD141" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -18090,7 +18098,7 @@
       </c>
       <c r="AD142" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -18160,7 +18168,7 @@
       </c>
       <c r="P143" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q143" s="2" t="inlineStr">
@@ -18284,7 +18292,7 @@
       </c>
       <c r="P144" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q144" s="2" t="inlineStr">
@@ -18328,17 +18336,17 @@
       </c>
       <c r="AB144" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC144" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD144" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18470,7 @@
       </c>
       <c r="AD145" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -18586,7 +18594,7 @@
       </c>
       <c r="AD146" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -18958,7 +18966,7 @@
       </c>
       <c r="AD149" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -19330,7 +19338,7 @@
       </c>
       <c r="AD152" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -19578,7 +19586,7 @@
       </c>
       <c r="AD154" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -19702,7 +19710,7 @@
       </c>
       <c r="AD155" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -19826,7 +19834,7 @@
       </c>
       <c r="AD156" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -19950,7 +19958,7 @@
       </c>
       <c r="AD157" s="2" t="inlineStr">
         <is>
-          <t>16/30</t>
+          <t>17/30</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20082,7 @@
       </c>
       <c r="AD158" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -20144,7 +20152,7 @@
       </c>
       <c r="P159" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q159" s="2" t="inlineStr">
@@ -20188,17 +20196,17 @@
       </c>
       <c r="AB159" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC159" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD159" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -20570,7 +20578,7 @@
       </c>
       <c r="AD162" s="2" t="inlineStr">
         <is>
-          <t>4/30</t>
+          <t>5/30</t>
         </is>
       </c>
     </row>
@@ -20694,7 +20702,7 @@
       </c>
       <c r="AD163" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -20942,7 +20950,7 @@
       </c>
       <c r="AD165" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -21322,7 +21330,7 @@
       </c>
       <c r="AD168" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -21562,7 +21570,7 @@
       </c>
       <c r="AD170" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -21686,7 +21694,7 @@
       </c>
       <c r="AD171" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -21756,7 +21764,7 @@
       </c>
       <c r="P172" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q172" s="2" t="inlineStr">
@@ -21805,12 +21813,12 @@
       </c>
       <c r="AC172" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD172" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -21934,7 +21942,7 @@
       </c>
       <c r="AD173" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -22004,7 +22012,7 @@
       </c>
       <c r="P174" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q174" s="2" t="inlineStr">
@@ -22053,12 +22061,12 @@
       </c>
       <c r="AC174" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD174" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -22128,7 +22136,7 @@
       </c>
       <c r="P175" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q175" s="2" t="inlineStr">
@@ -22172,17 +22180,17 @@
       </c>
       <c r="AB175" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC175" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD175" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -22306,7 +22314,7 @@
       </c>
       <c r="AD176" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -22500,7 +22508,7 @@
       </c>
       <c r="P178" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q178" s="2" t="inlineStr">
@@ -22544,17 +22552,17 @@
       </c>
       <c r="AB178" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC178" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD178" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -22624,7 +22632,7 @@
       </c>
       <c r="P179" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q179" s="2" t="inlineStr">
@@ -22678,7 +22686,7 @@
       </c>
       <c r="AD179" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -23050,7 +23058,7 @@
       </c>
       <c r="AD182" s="2" t="inlineStr">
         <is>
-          <t>21/30</t>
+          <t>24/30</t>
         </is>
       </c>
     </row>
@@ -23174,7 +23182,7 @@
       </c>
       <c r="AD183" s="2" t="inlineStr">
         <is>
-          <t>13/30</t>
+          <t>14/30</t>
         </is>
       </c>
     </row>
@@ -23298,7 +23306,7 @@
       </c>
       <c r="AD184" s="2" t="inlineStr">
         <is>
-          <t>14/30</t>
+          <t>15/30</t>
         </is>
       </c>
     </row>
@@ -23422,7 +23430,7 @@
       </c>
       <c r="AD185" s="2" t="inlineStr">
         <is>
-          <t>11/30</t>
+          <t>12/30</t>
         </is>
       </c>
     </row>
@@ -23546,7 +23554,7 @@
       </c>
       <c r="AD186" s="2" t="inlineStr">
         <is>
-          <t>12/30</t>
+          <t>13/30</t>
         </is>
       </c>
     </row>
@@ -23736,7 +23744,7 @@
       </c>
       <c r="P188" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q188" s="2" t="inlineStr">
@@ -23914,7 +23922,7 @@
       </c>
       <c r="AD189" s="2" t="inlineStr">
         <is>
-          <t>10/30</t>
+          <t>11/30</t>
         </is>
       </c>
     </row>
@@ -24154,7 +24162,7 @@
       </c>
       <c r="AD191" s="2" t="inlineStr">
         <is>
-          <t>18/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -24278,7 +24286,7 @@
       </c>
       <c r="AD192" s="2" t="inlineStr">
         <is>
-          <t>15/30</t>
+          <t>16/30</t>
         </is>
       </c>
     </row>
@@ -24410,7 +24418,7 @@
       </c>
       <c r="AD193" s="2" t="inlineStr">
         <is>
-          <t>17/30</t>
+          <t>19/30</t>
         </is>
       </c>
     </row>
@@ -24534,7 +24542,7 @@
       </c>
       <c r="AD194" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>25/30</t>
         </is>
       </c>
     </row>
@@ -24577,24 +24585,24 @@
       </c>
       <c r="I195" s="2" t="inlineStr">
         <is>
-          <t>21:35</t>
+          <t>21:33</t>
         </is>
       </c>
       <c r="J195" s="2" t="inlineStr">
         <is>
-          <t>135分钟</t>
+          <t>133分钟</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
       <c r="M195" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N195" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O195" s="2" t="inlineStr">
@@ -24604,7 +24612,7 @@
       </c>
       <c r="P195" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="Q195" s="2" t="inlineStr">
@@ -24653,12 +24661,12 @@
       </c>
       <c r="AC195" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>144.5</t>
         </is>
       </c>
       <c r="AD195" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>23/30</t>
         </is>
       </c>
     </row>
@@ -24914,7 +24922,7 @@
       </c>
       <c r="AD197" s="2" t="inlineStr">
         <is>
-          <t>19/30</t>
+          <t>22/30</t>
         </is>
       </c>
     </row>
@@ -24947,32 +24955,36 @@
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:46</t>
         </is>
       </c>
       <c r="J198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>126分钟</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
       <c r="M198" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N198" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="N198" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -24980,7 +24992,7 @@
       </c>
       <c r="P198" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q198" s="2" t="inlineStr">
@@ -25004,17 +25016,17 @@
       </c>
       <c r="X198" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y198" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z198" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA198" s="2" t="inlineStr">
@@ -25024,17 +25036,17 @@
       </c>
       <c r="AB198" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC198" s="2" t="inlineStr">
         <is>
-          <t>136.7</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="AD198" s="2" t="inlineStr">
         <is>
-          <t>5/30</t>
+          <t>4/30</t>
         </is>
       </c>
     </row>
@@ -25077,19 +25089,19 @@
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>21:51</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="J199" s="2" t="inlineStr">
         <is>
-          <t>131分钟</t>
+          <t>125分钟</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
       <c r="M199" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="N199" s="2" t="inlineStr">
@@ -25104,7 +25116,7 @@
       </c>
       <c r="P199" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="Q199" s="2" t="inlineStr">
@@ -25153,12 +25165,12 @@
       </c>
       <c r="AC199" s="2" t="inlineStr">
         <is>
-          <t>143.0</t>
+          <t>141.5</t>
         </is>
       </c>
       <c r="AD199" s="2" t="inlineStr">
         <is>
-          <t>20/30</t>
+          <t>18/30</t>
         </is>
       </c>
     </row>
@@ -25191,32 +25203,36 @@
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="J200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>118分钟</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
       <c r="M200" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N200" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N200" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
           <t>07:31</t>
@@ -25224,7 +25240,7 @@
       </c>
       <c r="P200" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q200" s="2" t="inlineStr">
@@ -25248,17 +25264,17 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z200" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA200" s="2" t="inlineStr">
@@ -25268,17 +25284,17 @@
       </c>
       <c r="AB200" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC200" s="2" t="inlineStr">
         <is>
-          <t>145.0</t>
+          <t>138.2</t>
         </is>
       </c>
       <c r="AD200" s="2" t="inlineStr">
         <is>
-          <t>22/30</t>
+          <t>9/30</t>
         </is>
       </c>
     </row>
@@ -25311,32 +25327,36 @@
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:07</t>
         </is>
       </c>
       <c r="J201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>122分钟</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
       <c r="M201" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N201" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N201" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
           <t>06:11</t>
@@ -25344,7 +25364,7 @@
       </c>
       <c r="P201" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q201" s="2" t="inlineStr">
@@ -25368,17 +25388,17 @@
       </c>
       <c r="X201" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y201" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z201" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA201" s="2" t="inlineStr">
@@ -25388,17 +25408,17 @@
       </c>
       <c r="AB201" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AC201" s="2" t="inlineStr">
         <is>
-          <t>148.7</t>
+          <t>142.0</t>
         </is>
       </c>
       <c r="AD201" s="2" t="inlineStr">
         <is>
-          <t>26/30</t>
+          <t>20/30</t>
         </is>
       </c>
     </row>
@@ -25464,7 +25484,7 @@
       </c>
       <c r="P202" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q202" s="2" t="inlineStr">
@@ -25518,7 +25538,7 @@
       </c>
       <c r="AD202" s="2" t="inlineStr">
         <is>
-          <t>25/30</t>
+          <t>26/30</t>
         </is>
       </c>
     </row>
@@ -25584,7 +25604,7 @@
       </c>
       <c r="P203" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:51</t>
         </is>
       </c>
       <c r="Q203" s="2" t="inlineStr">
@@ -26254,7 +26274,7 @@
       </c>
       <c r="AD208" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -26320,7 +26340,7 @@
       </c>
       <c r="P209" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q209" s="2" t="inlineStr">
@@ -26369,7 +26389,7 @@
       </c>
       <c r="AC209" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD209" s="2" t="inlineStr">
@@ -26692,7 +26712,7 @@
       </c>
       <c r="P212" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q212" s="2" t="inlineStr">
@@ -26736,17 +26756,17 @@
       </c>
       <c r="AB212" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC212" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD212" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -27552,7 +27572,7 @@
       </c>
       <c r="P219" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q219" s="2" t="inlineStr">
@@ -28226,7 +28246,7 @@
       </c>
       <c r="AD224" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -28656,7 +28676,7 @@
       </c>
       <c r="P228" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q228" s="2" t="inlineStr">
@@ -28705,7 +28725,7 @@
       </c>
       <c r="AC228" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD228" s="2" t="inlineStr">
@@ -29024,7 +29044,7 @@
       </c>
       <c r="P231" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q231" s="2" t="inlineStr">
@@ -29068,17 +29088,17 @@
       </c>
       <c r="AB231" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC231" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD231" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -29636,7 +29656,7 @@
       </c>
       <c r="P236" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q236" s="2" t="inlineStr">
@@ -30194,7 +30214,7 @@
       </c>
       <c r="AD240" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -33368,7 +33388,7 @@
       </c>
       <c r="P266" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q266" s="2" t="inlineStr">
@@ -33417,7 +33437,7 @@
       </c>
       <c r="AC266" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD266" s="2" t="inlineStr">
@@ -33616,7 +33636,7 @@
       </c>
       <c r="P268" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q268" s="2" t="inlineStr">
@@ -33660,17 +33680,17 @@
       </c>
       <c r="AB268" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC268" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD268" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -34038,7 +34058,7 @@
       </c>
       <c r="AD271" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -34108,7 +34128,7 @@
       </c>
       <c r="P272" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q272" s="2" t="inlineStr">
@@ -35592,7 +35612,7 @@
       </c>
       <c r="P284" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q284" s="2" t="inlineStr">
@@ -35641,7 +35661,7 @@
       </c>
       <c r="AC284" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD284" s="2" t="inlineStr">
@@ -35716,7 +35736,7 @@
       </c>
       <c r="P285" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q285" s="2" t="inlineStr">
@@ -35760,17 +35780,17 @@
       </c>
       <c r="AB285" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC285" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD285" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -36084,7 +36104,7 @@
       </c>
       <c r="P288" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q288" s="2" t="inlineStr">
@@ -36262,7 +36282,7 @@
       </c>
       <c r="AD289" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37568,7 +37588,7 @@
       </c>
       <c r="P300" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q300" s="2" t="inlineStr">
@@ -37617,7 +37637,7 @@
       </c>
       <c r="AC300" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD300" s="2" t="inlineStr">
@@ -37746,7 +37766,7 @@
       </c>
       <c r="AD301" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -37816,7 +37836,7 @@
       </c>
       <c r="P302" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q302" s="2" t="inlineStr">
@@ -37860,17 +37880,17 @@
       </c>
       <c r="AB302" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC302" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD302" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -38064,7 +38084,7 @@
       </c>
       <c r="P304" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q304" s="2" t="inlineStr">
@@ -38285,12 +38305,12 @@
       </c>
       <c r="I306" s="2" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:56</t>
         </is>
       </c>
       <c r="J306" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="K306" s="2" t="inlineStr"/>
@@ -38312,7 +38332,7 @@
       </c>
       <c r="P306" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="Q306" s="2" t="inlineStr">
@@ -38361,7 +38381,7 @@
       </c>
       <c r="AC306" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AD306" s="2" t="inlineStr">
@@ -38399,32 +38419,36 @@
       </c>
       <c r="G307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="H307" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="I307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="J307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="K307" s="2" t="inlineStr"/>
       <c r="L307" s="2" t="inlineStr"/>
       <c r="M307" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="N307" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="N307" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="O307" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -38432,7 +38456,7 @@
       </c>
       <c r="P307" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q307" s="2" t="inlineStr">
@@ -38456,17 +38480,17 @@
       </c>
       <c r="X307" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="Y307" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Z307" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="AA307" s="2" t="inlineStr">
@@ -38476,17 +38500,17 @@
       </c>
       <c r="AB307" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AC307" s="2" t="inlineStr">
         <is>
-          <t>95.2</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AD307" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -38552,7 +38576,7 @@
       </c>
       <c r="P308" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="Q308" s="2" t="inlineStr">
